--- a/finance/output/Payment_Companies_Financial_Metrics_20250506_153346.xlsx
+++ b/finance/output/Payment_Companies_Financial_Metrics_20250506_153346.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\code\finance_script\finance\output\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C67350FF-392F-4907-8DC9-6E7F2B463A8A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F8EAB9F-47D2-459A-93AA-82483BBBB198}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -614,6 +614,8 @@
     <col min="11" max="11" width="20.86328125" customWidth="1"/>
     <col min="12" max="12" width="21.6640625" customWidth="1"/>
     <col min="13" max="13" width="24.06640625" customWidth="1"/>
+    <col min="14" max="14" width="33.796875" customWidth="1"/>
+    <col min="15" max="15" width="31.19921875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.3">
